--- a/docs/tables/summary_all_objects_accuracy_f1_EN.xlsx
+++ b/docs/tables/summary_all_objects_accuracy_f1_EN.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="significance" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,6 +32,14 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00585D54"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000D8054"/>
     </font>
   </fonts>
   <fills count="3">
@@ -63,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -80,6 +89,8 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z25"/>
+  <dimension ref="A1:AF25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -470,10 +481,16 @@
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="15" customWidth="1" min="23" max="23"/>
-    <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="60" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="60" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -584,25 +601,55 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>F1@3cm CI low</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>F1@3cm CI high</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy@3cm CI low</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy@3cm CI high</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>completeness@3cm CI low</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>completeness@3cm CI high</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>raw points</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>matched points (1cm voxel)</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>raw/matched ratio</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>DBSCAN mode</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>reference note</t>
         </is>
@@ -679,20 +726,38 @@
         <v>49.7</v>
       </c>
       <c r="V2" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="X2" s="4" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="Y2" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z2" s="4" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="AA2" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="AB2" s="4" t="n">
         <v>624826</v>
       </c>
-      <c r="W2" s="4" t="n">
+      <c r="AC2" s="4" t="n">
         <v>118844</v>
       </c>
-      <c r="X2" s="4" t="n">
+      <c r="AD2" s="4" t="n">
         <v>5.26</v>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
+      <c r="AE2" s="3" t="inlineStr">
         <is>
           <t>ft10/eps3/mp5</t>
         </is>
       </c>
-      <c r="Z2" s="5" t="inlineStr">
+      <c r="AF2" s="5" t="inlineStr">
         <is>
           <t>incomplete reference: the bus stop's far side (away from the road) wasn't scanned; part of the reference is a merge of 2 scans that don't align perfectly in places</t>
         </is>
@@ -747,12 +812,30 @@
         <v>51.2</v>
       </c>
       <c r="V3" t="n">
+        <v>43</v>
+      </c>
+      <c r="W3" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="AB3" t="n">
         <v>789125</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AC3" t="n">
         <v>139982</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AD3" t="n">
         <v>5.64</v>
       </c>
     </row>
@@ -805,12 +888,30 @@
         <v>42.3</v>
       </c>
       <c r="V4" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="W4" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="X4" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1150918</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AC4" t="n">
         <v>458520</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AD4" t="n">
         <v>2.51</v>
       </c>
     </row>
@@ -863,12 +964,30 @@
         <v>55.5</v>
       </c>
       <c r="V5" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="X5" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>96</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="AB5" t="n">
         <v>6995057</v>
       </c>
-      <c r="W5" t="n">
+      <c r="AC5" t="n">
         <v>2432352</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AD5" t="n">
         <v>2.88</v>
       </c>
     </row>
@@ -943,20 +1062,38 @@
         <v>14.5</v>
       </c>
       <c r="V6" s="4" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="W6" s="4" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="X6" s="4" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="Y6" s="4" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="Z6" s="4" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="AA6" s="4" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="AB6" s="4" t="n">
         <v>1123433</v>
       </c>
-      <c r="W6" s="4" t="n">
+      <c r="AC6" s="4" t="n">
         <v>36738</v>
       </c>
-      <c r="X6" s="4" t="n">
+      <c r="AD6" s="4" t="n">
         <v>30.58</v>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
+      <c r="AE6" s="3" t="inlineStr">
         <is>
           <t>ft5/eps2/mp3</t>
         </is>
       </c>
-      <c r="Z6" s="5" t="inlineStr">
+      <c r="AF6" s="5" t="inlineStr">
         <is>
           <t>incomplete reference: only the upper ~2/3 of the pole height and one side were scanned — comparison is only valid in that region (not a scale/rotation error)</t>
         </is>
@@ -1011,12 +1148,30 @@
         <v>18.2</v>
       </c>
       <c r="V7" t="n">
+        <v>79</v>
+      </c>
+      <c r="W7" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="X7" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1064834</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AC7" t="n">
         <v>37804</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AD7" t="n">
         <v>28.17</v>
       </c>
     </row>
@@ -1069,12 +1224,30 @@
         <v>11.5</v>
       </c>
       <c r="V8" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="W8" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="X8" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="AB8" t="n">
         <v>734656</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AC8" t="n">
         <v>70153</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AD8" t="n">
         <v>10.47</v>
       </c>
     </row>
@@ -1127,12 +1300,30 @@
         <v>30</v>
       </c>
       <c r="V9" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>99</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="AB9" t="n">
         <v>3334257</v>
       </c>
-      <c r="W9" t="n">
+      <c r="AC9" t="n">
         <v>161957</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AD9" t="n">
         <v>20.59</v>
       </c>
     </row>
@@ -1207,20 +1398,38 @@
         <v>24.8</v>
       </c>
       <c r="V10" s="4" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="W10" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="X10" s="4" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="Y10" s="4" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="Z10" s="4" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AA10" s="4" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="AB10" s="4" t="n">
         <v>1520520</v>
       </c>
-      <c r="W10" s="4" t="n">
+      <c r="AC10" s="4" t="n">
         <v>115064</v>
       </c>
-      <c r="X10" s="4" t="n">
+      <c r="AD10" s="4" t="n">
         <v>13.21</v>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
+      <c r="AE10" s="3" t="inlineStr">
         <is>
           <t>ft5/eps3/mp2</t>
         </is>
       </c>
-      <c r="Z10" s="5" t="inlineStr">
+      <c r="AF10" s="5" t="inlineStr">
         <is>
           <t>incomplete reference: the bench's backrest (rear side) and legs are missing</t>
         </is>
@@ -1275,12 +1484,30 @@
         <v>36.2</v>
       </c>
       <c r="V11" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="W11" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1462675</v>
       </c>
-      <c r="W11" t="n">
+      <c r="AC11" t="n">
         <v>103983</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AD11" t="n">
         <v>14.07</v>
       </c>
     </row>
@@ -1333,12 +1560,30 @@
         <v>29.7</v>
       </c>
       <c r="V12" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="W12" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="X12" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AB12" t="n">
         <v>804316</v>
       </c>
-      <c r="W12" t="n">
+      <c r="AC12" t="n">
         <v>136786</v>
       </c>
-      <c r="X12" t="n">
+      <c r="AD12" t="n">
         <v>5.88</v>
       </c>
     </row>
@@ -1391,12 +1636,30 @@
         <v>32.5</v>
       </c>
       <c r="V13" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="W13" t="n">
+        <v>68</v>
+      </c>
+      <c r="X13" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="AB13" t="n">
         <v>6726594</v>
       </c>
-      <c r="W13" t="n">
+      <c r="AC13" t="n">
         <v>359926</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AD13" t="n">
         <v>18.69</v>
       </c>
     </row>
@@ -1471,20 +1734,38 @@
         <v>16.1</v>
       </c>
       <c r="V14" s="4" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="W14" s="4" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="X14" s="4" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="Y14" s="4" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="Z14" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="AA14" s="4" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="AB14" s="4" t="n">
         <v>214105</v>
       </c>
-      <c r="W14" s="4" t="n">
+      <c r="AC14" s="4" t="n">
         <v>6021</v>
       </c>
-      <c r="X14" s="4" t="n">
+      <c r="AD14" s="4" t="n">
         <v>35.56</v>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
+      <c r="AE14" s="3" t="inlineStr">
         <is>
           <t>ft5/eps2/mp3</t>
         </is>
       </c>
-      <c r="Z14" s="5" t="inlineStr">
+      <c r="AF14" s="5" t="inlineStr">
         <is>
           <t>incomplete reference: only one side was scanned (~90° sector missing) — the missing side is handled via gap detection (DBSCAN)</t>
         </is>
@@ -1539,12 +1820,30 @@
         <v>10.9</v>
       </c>
       <c r="V15" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="W15" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="X15" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>91</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="AB15" t="n">
         <v>308184</v>
       </c>
-      <c r="W15" t="n">
+      <c r="AC15" t="n">
         <v>7106</v>
       </c>
-      <c r="X15" t="n">
+      <c r="AD15" t="n">
         <v>43.37</v>
       </c>
     </row>
@@ -1597,12 +1896,30 @@
         <v>6</v>
       </c>
       <c r="V16" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="W16" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>89</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>98</v>
+      </c>
+      <c r="AB16" t="n">
         <v>533608</v>
       </c>
-      <c r="W16" t="n">
+      <c r="AC16" t="n">
         <v>14002</v>
       </c>
-      <c r="X16" t="n">
+      <c r="AD16" t="n">
         <v>38.11</v>
       </c>
     </row>
@@ -1655,12 +1972,30 @@
         <v>8.6</v>
       </c>
       <c r="V17" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="W17" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="X17" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>98</v>
+      </c>
+      <c r="AB17" t="n">
         <v>3697595</v>
       </c>
-      <c r="W17" t="n">
+      <c r="AC17" t="n">
         <v>28592</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AD17" t="n">
         <v>129.32</v>
       </c>
     </row>
@@ -1735,20 +2070,38 @@
         <v>9.800000000000001</v>
       </c>
       <c r="V18" s="4" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="W18" s="4" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="X18" s="4" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="Y18" s="4" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="Z18" s="4" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="AA18" s="4" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="AB18" s="4" t="n">
         <v>133185</v>
       </c>
-      <c r="W18" s="4" t="n">
+      <c r="AC18" s="4" t="n">
         <v>18583</v>
       </c>
-      <c r="X18" s="4" t="n">
+      <c r="AD18" s="4" t="n">
         <v>7.17</v>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
+      <c r="AE18" s="3" t="inlineStr">
         <is>
           <t>no DBSCAN</t>
         </is>
       </c>
-      <c r="Z18" s="5" t="inlineStr">
+      <c r="AF18" s="5" t="inlineStr">
         <is>
           <t>full reference</t>
         </is>
@@ -1803,12 +2156,30 @@
         <v>11.5</v>
       </c>
       <c r="V19" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="X19" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="AB19" t="n">
         <v>59502</v>
       </c>
-      <c r="W19" t="n">
+      <c r="AC19" t="n">
         <v>10543</v>
       </c>
-      <c r="X19" t="n">
+      <c r="AD19" t="n">
         <v>5.64</v>
       </c>
     </row>
@@ -1861,12 +2232,30 @@
         <v>34</v>
       </c>
       <c r="V20" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="X20" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="AB20" t="n">
         <v>177102</v>
       </c>
-      <c r="W20" t="n">
+      <c r="AC20" t="n">
         <v>46577</v>
       </c>
-      <c r="X20" t="n">
+      <c r="AD20" t="n">
         <v>3.8</v>
       </c>
     </row>
@@ -1919,12 +2308,30 @@
         <v>41.6</v>
       </c>
       <c r="V21" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="AB21" t="n">
         <v>293168</v>
       </c>
-      <c r="W21" t="n">
+      <c r="AC21" t="n">
         <v>152549</v>
       </c>
-      <c r="X21" t="n">
+      <c r="AD21" t="n">
         <v>1.92</v>
       </c>
     </row>
@@ -1999,20 +2406,38 @@
         <v>27.2</v>
       </c>
       <c r="V22" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="W22" s="4" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="X22" s="4" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="Y22" s="4" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="Z22" s="4" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="AA22" s="4" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="AB22" s="4" t="n">
         <v>327676</v>
       </c>
-      <c r="W22" s="4" t="n">
+      <c r="AC22" s="4" t="n">
         <v>29266</v>
       </c>
-      <c r="X22" s="4" t="n">
+      <c r="AD22" s="4" t="n">
         <v>11.2</v>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
+      <c r="AE22" s="3" t="inlineStr">
         <is>
           <t>no DBSCAN</t>
         </is>
       </c>
-      <c r="Z22" s="5" t="inlineStr">
+      <c r="AF22" s="5" t="inlineStr">
         <is>
           <t>full reference</t>
         </is>
@@ -2067,12 +2492,30 @@
         <v>34.9</v>
       </c>
       <c r="V23" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="W23" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="AB23" t="n">
         <v>261293</v>
       </c>
-      <c r="W23" t="n">
+      <c r="AC23" t="n">
         <v>23147</v>
       </c>
-      <c r="X23" t="n">
+      <c r="AD23" t="n">
         <v>11.29</v>
       </c>
     </row>
@@ -2125,12 +2568,30 @@
         <v>27.2</v>
       </c>
       <c r="V24" t="n">
+        <v>41</v>
+      </c>
+      <c r="W24" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="X24" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="AB24" t="n">
         <v>569403</v>
       </c>
-      <c r="W24" t="n">
+      <c r="AC24" t="n">
         <v>130311</v>
       </c>
-      <c r="X24" t="n">
+      <c r="AD24" t="n">
         <v>4.37</v>
       </c>
     </row>
@@ -2183,12 +2644,30 @@
         <v>37</v>
       </c>
       <c r="V25" t="n">
+        <v>51</v>
+      </c>
+      <c r="W25" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="X25" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="AB25" t="n">
         <v>2881563</v>
       </c>
-      <c r="W25" t="n">
+      <c r="AC25" t="n">
         <v>322936</v>
       </c>
-      <c r="X25" t="n">
+      <c r="AD25" t="n">
         <v>8.92</v>
       </c>
     </row>
@@ -2199,50 +2678,1233 @@
     <mergeCell ref="B22:B25"/>
     <mergeCell ref="E14:E17"/>
     <mergeCell ref="D22:D25"/>
+    <mergeCell ref="AE22:AE25"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="D6:D9"/>
+    <mergeCell ref="AF18:AF21"/>
     <mergeCell ref="F6:F9"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="C10:C13"/>
+    <mergeCell ref="AE2:AE5"/>
     <mergeCell ref="D2:D5"/>
     <mergeCell ref="E10:E13"/>
+    <mergeCell ref="AF10:AF13"/>
     <mergeCell ref="B14:B17"/>
-    <mergeCell ref="Y14:Y17"/>
+    <mergeCell ref="AE18:AE21"/>
     <mergeCell ref="C22:C25"/>
     <mergeCell ref="F18:F21"/>
-    <mergeCell ref="Z22:Z25"/>
     <mergeCell ref="C18:C21"/>
-    <mergeCell ref="Z18:Z21"/>
+    <mergeCell ref="AE14:AE17"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="F2:F5"/>
     <mergeCell ref="E6:E9"/>
-    <mergeCell ref="Y2:Y5"/>
-    <mergeCell ref="Z2:Z5"/>
-    <mergeCell ref="Y10:Y13"/>
+    <mergeCell ref="AF6:AF9"/>
     <mergeCell ref="B10:B13"/>
-    <mergeCell ref="Y6:Y9"/>
+    <mergeCell ref="AE10:AE13"/>
     <mergeCell ref="A18:A21"/>
     <mergeCell ref="F22:F25"/>
-    <mergeCell ref="Z14:Z17"/>
     <mergeCell ref="D18:D21"/>
-    <mergeCell ref="Y22:Y25"/>
+    <mergeCell ref="AF14:AF17"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="C2:C5"/>
+    <mergeCell ref="AF2:AF5"/>
+    <mergeCell ref="E2:E5"/>
     <mergeCell ref="B6:B9"/>
-    <mergeCell ref="E2:E5"/>
     <mergeCell ref="A14:A17"/>
-    <mergeCell ref="Z10:Z13"/>
+    <mergeCell ref="AE6:AE9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A22:A25"/>
     <mergeCell ref="D14:D17"/>
     <mergeCell ref="E22:E25"/>
     <mergeCell ref="F14:F17"/>
-    <mergeCell ref="Z6:Z9"/>
-    <mergeCell ref="Y18:Y21"/>
+    <mergeCell ref="AF22:AF25"/>
     <mergeCell ref="C6:C9"/>
     <mergeCell ref="D10:D13"/>
     <mergeCell ref="F10:F13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Pairwise F1@3cm differences between methods on the same object, 2000 spatial block-bootstrap draws, 5 cm blocks. Unpaired: the four reconstructions of an object are independent clouds with no frames in common. A CI spanning 0 means the two methods are not distinguishable on that object.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>object_id</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>method A</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>method B</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>ΔF1@3cm (pp)</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>95% CI low</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>95% CI high</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>resolvable?</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bus_stop_002</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bus_stop_002</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-10.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>bus_stop_002</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>bus_stop_002</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-13</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-14.4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-11.7</v>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>bus_stop_002</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>bus_stop_002</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>14</v>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="E14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>13</v>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>information_sign_002</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="F15" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>bench_004</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11</v>
+      </c>
+      <c r="E16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F16" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>bench_004</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>bench_004</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>bench_004</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-12.9</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-11.4</v>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>bench_004</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-11.3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>bench_004</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>no - CI spans 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>bollard_003</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>flashlight_004</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F28" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>flashlight_004</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E29" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>flashlight_004</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="E30" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>flashlight_004</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>flashlight_004</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="E32" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>flashlight_004</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>35</v>
+      </c>
+      <c r="F33" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>bus_stop_sign_002</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E34" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>bus_stop_sign_002</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E35" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F35" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>bus_stop_sign_002</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>colmap</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="E36" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F36" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>bus_stop_sign_002</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="E37" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>bus_stop_sign_002</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>hloc_colmap</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F38" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>bus_stop_sign_002</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>mast3r_ga</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>vggt</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/tables/summary_all_objects_accuracy_f1_EN.xlsx
+++ b/docs/tables/summary_all_objects_accuracy_f1_EN.xlsx
@@ -165,6 +165,24 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>build_accuracy_f1_summary_table.py</author>
+  </authors>
+  <commentList>
+    <comment ref="AD1" authorId="0" shapeId="0">
+      <text>
+        <t>Symmetric Chamfer distance, in centimetres.
+Convention used here: the mean of the two one-sided means - reconstruction to reference (the accuracy side) and reference to reconstruction (the completeness side) - with the distances NOT squared, on the same 1 cm grid and the same gap-excluded points as every other column. Accuracy and completeness are those two halves; this is their half-sum.
+Papers on learned reconstruction (VGGT and MASt3R included) commonly report a SQUARED Chamfer, so their numbers are not directly comparable with these.
+Reported for completeness. The thresholded F1 columns remain the primary result: where the reference itself is incomplete, a raw symmetric distance is dominated by the regions the scanner never reached rather than by the quality of the reconstruction.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -456,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF25"/>
+  <dimension ref="A1:AI25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -486,11 +504,14 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
     <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="12" customWidth="1" min="28" max="28"/>
-    <col width="15" customWidth="1" min="29" max="29"/>
-    <col width="13" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="60" customWidth="1" min="32" max="32"/>
+    <col width="16" customWidth="1" min="28" max="28"/>
+    <col width="19" customWidth="1" min="29" max="29"/>
+    <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="15" customWidth="1" min="32" max="32"/>
+    <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="14" customWidth="1" min="34" max="34"/>
+    <col width="60" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -541,7 +562,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>alignment RMSE (mm)</t>
+          <t>alignment RMSE (cm)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -631,25 +652,40 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>accuracy mean (cm)</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>completeness mean (cm)</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>symmetric Chamfer (cm)</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
           <t>raw points</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>matched points (1cm voxel)</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>raw/matched ratio</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>DBSCAN mode</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>reference note</t>
         </is>
@@ -690,7 +726,7 @@
         <v>4.03</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>19.28</v>
+        <v>1.93</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>50.6</v>
@@ -744,20 +780,29 @@
         <v>40.6</v>
       </c>
       <c r="AB2" s="4" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AC2" s="4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AD2" s="4" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="AE2" s="4" t="n">
         <v>624826</v>
       </c>
-      <c r="AC2" s="4" t="n">
+      <c r="AF2" s="4" t="n">
         <v>118844</v>
       </c>
-      <c r="AD2" s="4" t="n">
+      <c r="AG2" s="4" t="n">
         <v>5.26</v>
       </c>
-      <c r="AE2" s="3" t="inlineStr">
+      <c r="AH2" s="3" t="inlineStr">
         <is>
           <t>ft10/eps3/mp5</t>
         </is>
       </c>
-      <c r="AF2" s="5" t="inlineStr">
+      <c r="AI2" s="5" t="inlineStr">
         <is>
           <t>incomplete reference: the bus stop's far side (away from the road) wasn't scanned; part of the reference is a merge of 2 scans that don't align perfectly in places</t>
         </is>
@@ -776,7 +821,7 @@
         <v>3.7</v>
       </c>
       <c r="J3" t="n">
-        <v>19.75</v>
+        <v>1.98</v>
       </c>
       <c r="K3" t="n">
         <v>42.8</v>
@@ -830,12 +875,21 @@
         <v>42.1</v>
       </c>
       <c r="AB3" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AE3" t="n">
         <v>789125</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AF3" t="n">
         <v>139982</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AG3" t="n">
         <v>5.64</v>
       </c>
     </row>
@@ -852,7 +906,7 @@
         <v>1.31</v>
       </c>
       <c r="J4" t="n">
-        <v>19.08</v>
+        <v>1.91</v>
       </c>
       <c r="K4" t="n">
         <v>38.7</v>
@@ -906,12 +960,21 @@
         <v>80.5</v>
       </c>
       <c r="AB4" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1150918</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AF4" t="n">
         <v>458520</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AG4" t="n">
         <v>2.51</v>
       </c>
     </row>
@@ -928,7 +991,7 @@
         <v>0.71</v>
       </c>
       <c r="J5" t="n">
-        <v>20.04</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>18.7</v>
@@ -982,12 +1045,21 @@
         <v>96.8</v>
       </c>
       <c r="AB5" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AE5" t="n">
         <v>6995057</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AF5" t="n">
         <v>2432352</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AG5" t="n">
         <v>2.88</v>
       </c>
     </row>
@@ -1026,7 +1098,7 @@
         <v>0.58</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>14.82</v>
+        <v>1.48</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>40.5</v>
@@ -1080,20 +1152,29 @@
         <v>91.7</v>
       </c>
       <c r="AB6" s="4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC6" s="4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD6" s="4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE6" s="4" t="n">
         <v>1123433</v>
       </c>
-      <c r="AC6" s="4" t="n">
+      <c r="AF6" s="4" t="n">
         <v>36738</v>
       </c>
-      <c r="AD6" s="4" t="n">
+      <c r="AG6" s="4" t="n">
         <v>30.58</v>
       </c>
-      <c r="AE6" s="3" t="inlineStr">
+      <c r="AH6" s="3" t="inlineStr">
         <is>
           <t>ft5/eps2/mp3</t>
         </is>
       </c>
-      <c r="AF6" s="5" t="inlineStr">
+      <c r="AI6" s="5" t="inlineStr">
         <is>
           <t>incomplete reference: only the upper ~2/3 of the pole height and one side were scanned — comparison is only valid in that region (not a scale/rotation error)</t>
         </is>
@@ -1112,7 +1193,7 @@
         <v>0.91</v>
       </c>
       <c r="J7" t="n">
-        <v>15.7</v>
+        <v>1.57</v>
       </c>
       <c r="K7" t="n">
         <v>35.6</v>
@@ -1166,12 +1247,21 @@
         <v>88.8</v>
       </c>
       <c r="AB7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1064834</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AF7" t="n">
         <v>37804</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AG7" t="n">
         <v>28.17</v>
       </c>
     </row>
@@ -1188,7 +1278,7 @@
         <v>0.64</v>
       </c>
       <c r="J8" t="n">
-        <v>16.09</v>
+        <v>1.61</v>
       </c>
       <c r="K8" t="n">
         <v>42.3</v>
@@ -1242,12 +1332,21 @@
         <v>99.5</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE8" t="n">
         <v>734656</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AF8" t="n">
         <v>70153</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AG8" t="n">
         <v>10.47</v>
       </c>
     </row>
@@ -1264,7 +1363,7 @@
         <v>0.63</v>
       </c>
       <c r="J9" t="n">
-        <v>19.77</v>
+        <v>1.98</v>
       </c>
       <c r="K9" t="n">
         <v>24.2</v>
@@ -1318,12 +1417,21 @@
         <v>99.8</v>
       </c>
       <c r="AB9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE9" t="n">
         <v>3334257</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AF9" t="n">
         <v>161957</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AG9" t="n">
         <v>20.59</v>
       </c>
     </row>
@@ -1362,7 +1470,7 @@
         <v>1.69</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>19.87</v>
+        <v>1.99</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>56.2</v>
@@ -1416,20 +1524,29 @@
         <v>69.09999999999999</v>
       </c>
       <c r="AB10" s="4" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AC10" s="4" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="AD10" s="4" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AE10" s="4" t="n">
         <v>1520520</v>
       </c>
-      <c r="AC10" s="4" t="n">
+      <c r="AF10" s="4" t="n">
         <v>115064</v>
       </c>
-      <c r="AD10" s="4" t="n">
+      <c r="AG10" s="4" t="n">
         <v>13.21</v>
       </c>
-      <c r="AE10" s="3" t="inlineStr">
+      <c r="AH10" s="3" t="inlineStr">
         <is>
           <t>ft5/eps3/mp2</t>
         </is>
       </c>
-      <c r="AF10" s="5" t="inlineStr">
+      <c r="AI10" s="5" t="inlineStr">
         <is>
           <t>incomplete reference: the bench's backrest (rear side) and legs are missing</t>
         </is>
@@ -1448,7 +1565,7 @@
         <v>2.8</v>
       </c>
       <c r="J11" t="n">
-        <v>21.7</v>
+        <v>2.17</v>
       </c>
       <c r="K11" t="n">
         <v>50.5</v>
@@ -1502,12 +1619,21 @@
         <v>56.5</v>
       </c>
       <c r="AB11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1462675</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AF11" t="n">
         <v>103983</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AG11" t="n">
         <v>14.07</v>
       </c>
     </row>
@@ -1524,7 +1650,7 @@
         <v>1.48</v>
       </c>
       <c r="J12" t="n">
-        <v>19.55</v>
+        <v>1.96</v>
       </c>
       <c r="K12" t="n">
         <v>56.1</v>
@@ -1578,12 +1704,21 @@
         <v>73.59999999999999</v>
       </c>
       <c r="AB12" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AE12" t="n">
         <v>804316</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AF12" t="n">
         <v>136786</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AG12" t="n">
         <v>5.88</v>
       </c>
     </row>
@@ -1600,7 +1735,7 @@
         <v>1.11</v>
       </c>
       <c r="J13" t="n">
-        <v>20.86</v>
+        <v>2.09</v>
       </c>
       <c r="K13" t="n">
         <v>39.5</v>
@@ -1654,12 +1789,21 @@
         <v>85.8</v>
       </c>
       <c r="AB13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AE13" t="n">
         <v>6726594</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AF13" t="n">
         <v>359926</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AG13" t="n">
         <v>18.69</v>
       </c>
     </row>
@@ -1698,7 +1842,7 @@
         <v>1.21</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>12.68</v>
+        <v>1.27</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>68.2</v>
@@ -1752,20 +1896,29 @@
         <v>83.7</v>
       </c>
       <c r="AB14" s="4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC14" s="4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD14" s="4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE14" s="4" t="n">
         <v>214105</v>
       </c>
-      <c r="AC14" s="4" t="n">
+      <c r="AF14" s="4" t="n">
         <v>6021</v>
       </c>
-      <c r="AD14" s="4" t="n">
+      <c r="AG14" s="4" t="n">
         <v>35.56</v>
       </c>
-      <c r="AE14" s="3" t="inlineStr">
+      <c r="AH14" s="3" t="inlineStr">
         <is>
           <t>ft5/eps2/mp3</t>
         </is>
       </c>
-      <c r="AF14" s="5" t="inlineStr">
+      <c r="AI14" s="5" t="inlineStr">
         <is>
           <t>incomplete reference: only one side was scanned (~90° sector missing) — the missing side is handled via gap detection (DBSCAN)</t>
         </is>
@@ -1784,7 +1937,7 @@
         <v>0.89</v>
       </c>
       <c r="J15" t="n">
-        <v>12.19</v>
+        <v>1.22</v>
       </c>
       <c r="K15" t="n">
         <v>69.59999999999999</v>
@@ -1838,12 +1991,21 @@
         <v>92.2</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE15" t="n">
         <v>308184</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AF15" t="n">
         <v>7106</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AG15" t="n">
         <v>43.37</v>
       </c>
     </row>
@@ -1860,7 +2022,7 @@
         <v>0.61</v>
       </c>
       <c r="J16" t="n">
-        <v>12.82</v>
+        <v>1.28</v>
       </c>
       <c r="K16" t="n">
         <v>72.2</v>
@@ -1914,12 +2076,21 @@
         <v>98</v>
       </c>
       <c r="AB16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE16" t="n">
         <v>533608</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AF16" t="n">
         <v>14002</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AG16" t="n">
         <v>38.11</v>
       </c>
     </row>
@@ -1936,7 +2107,7 @@
         <v>0.63</v>
       </c>
       <c r="J17" t="n">
-        <v>14.65</v>
+        <v>1.47</v>
       </c>
       <c r="K17" t="n">
         <v>64</v>
@@ -1990,12 +2161,21 @@
         <v>98</v>
       </c>
       <c r="AB17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE17" t="n">
         <v>3697595</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AF17" t="n">
         <v>28592</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AG17" t="n">
         <v>129.32</v>
       </c>
     </row>
@@ -2034,7 +2214,7 @@
         <v>1.23</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>11.59</v>
+        <v>1.16</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>96.59999999999999</v>
@@ -2088,20 +2268,29 @@
         <v>85.40000000000001</v>
       </c>
       <c r="AB18" s="4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC18" s="4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD18" s="4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AE18" s="4" t="n">
         <v>133185</v>
       </c>
-      <c r="AC18" s="4" t="n">
+      <c r="AF18" s="4" t="n">
         <v>18583</v>
       </c>
-      <c r="AD18" s="4" t="n">
+      <c r="AG18" s="4" t="n">
         <v>7.17</v>
       </c>
-      <c r="AE18" s="3" t="inlineStr">
+      <c r="AH18" s="3" t="inlineStr">
         <is>
           <t>no DBSCAN</t>
         </is>
       </c>
-      <c r="AF18" s="5" t="inlineStr">
+      <c r="AI18" s="5" t="inlineStr">
         <is>
           <t>full reference</t>
         </is>
@@ -2120,7 +2309,7 @@
         <v>1.65</v>
       </c>
       <c r="J19" t="n">
-        <v>13</v>
+        <v>1.3</v>
       </c>
       <c r="K19" t="n">
         <v>91.7</v>
@@ -2174,12 +2363,21 @@
         <v>78.3</v>
       </c>
       <c r="AB19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AE19" t="n">
         <v>59502</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AF19" t="n">
         <v>10543</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AG19" t="n">
         <v>5.64</v>
       </c>
     </row>
@@ -2196,7 +2394,7 @@
         <v>1.32</v>
       </c>
       <c r="J20" t="n">
-        <v>16.84</v>
+        <v>1.68</v>
       </c>
       <c r="K20" t="n">
         <v>44.5</v>
@@ -2250,12 +2448,21 @@
         <v>90.59999999999999</v>
       </c>
       <c r="AB20" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AE20" t="n">
         <v>177102</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AF20" t="n">
         <v>46577</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AG20" t="n">
         <v>3.8</v>
       </c>
     </row>
@@ -2272,7 +2479,7 @@
         <v>1.17</v>
       </c>
       <c r="J21" t="n">
-        <v>17.59</v>
+        <v>1.76</v>
       </c>
       <c r="K21" t="n">
         <v>12.3</v>
@@ -2326,12 +2533,21 @@
         <v>97.2</v>
       </c>
       <c r="AB21" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="AE21" t="n">
         <v>293168</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AF21" t="n">
         <v>152549</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AG21" t="n">
         <v>1.92</v>
       </c>
     </row>
@@ -2370,7 +2586,7 @@
         <v>1.88</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>17.77</v>
+        <v>1.78</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>58.8</v>
@@ -2424,20 +2640,29 @@
         <v>80.59999999999999</v>
       </c>
       <c r="AB22" s="4" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AC22" s="4" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AD22" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE22" s="4" t="n">
         <v>327676</v>
       </c>
-      <c r="AC22" s="4" t="n">
+      <c r="AF22" s="4" t="n">
         <v>29266</v>
       </c>
-      <c r="AD22" s="4" t="n">
+      <c r="AG22" s="4" t="n">
         <v>11.2</v>
       </c>
-      <c r="AE22" s="3" t="inlineStr">
+      <c r="AH22" s="3" t="inlineStr">
         <is>
           <t>no DBSCAN</t>
         </is>
       </c>
-      <c r="AF22" s="5" t="inlineStr">
+      <c r="AI22" s="5" t="inlineStr">
         <is>
           <t>full reference</t>
         </is>
@@ -2456,7 +2681,7 @@
         <v>2.16</v>
       </c>
       <c r="J23" t="n">
-        <v>16.59</v>
+        <v>1.66</v>
       </c>
       <c r="K23" t="n">
         <v>52.7</v>
@@ -2510,12 +2735,21 @@
         <v>67.3</v>
       </c>
       <c r="AB23" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AE23" t="n">
         <v>261293</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AF23" t="n">
         <v>23147</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AG23" t="n">
         <v>11.29</v>
       </c>
     </row>
@@ -2532,7 +2766,7 @@
         <v>1.3</v>
       </c>
       <c r="J24" t="n">
-        <v>17.87</v>
+        <v>1.79</v>
       </c>
       <c r="K24" t="n">
         <v>28.6</v>
@@ -2586,12 +2820,21 @@
         <v>85.40000000000001</v>
       </c>
       <c r="AB24" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="AE24" t="n">
         <v>569403</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AF24" t="n">
         <v>130311</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AG24" t="n">
         <v>4.37</v>
       </c>
     </row>
@@ -2608,7 +2851,7 @@
         <v>0.58</v>
       </c>
       <c r="J25" t="n">
-        <v>18.17</v>
+        <v>1.82</v>
       </c>
       <c r="K25" t="n">
         <v>35.5</v>
@@ -2662,67 +2905,77 @@
         <v>99.7</v>
       </c>
       <c r="AB25" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AE25" t="n">
         <v>2881563</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AF25" t="n">
         <v>322936</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AG25" t="n">
         <v>8.92</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="AI10:AI13"/>
     <mergeCell ref="C14:C17"/>
     <mergeCell ref="E18:E21"/>
+    <mergeCell ref="E14:E17"/>
+    <mergeCell ref="AH18:AH21"/>
     <mergeCell ref="B22:B25"/>
-    <mergeCell ref="E14:E17"/>
     <mergeCell ref="D22:D25"/>
-    <mergeCell ref="AE22:AE25"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="D6:D9"/>
-    <mergeCell ref="AF18:AF21"/>
     <mergeCell ref="F6:F9"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="C10:C13"/>
-    <mergeCell ref="AE2:AE5"/>
+    <mergeCell ref="AI6:AI9"/>
     <mergeCell ref="D2:D5"/>
     <mergeCell ref="E10:E13"/>
-    <mergeCell ref="AF10:AF13"/>
+    <mergeCell ref="AH14:AH17"/>
+    <mergeCell ref="AH10:AH13"/>
     <mergeCell ref="B14:B17"/>
-    <mergeCell ref="AE18:AE21"/>
     <mergeCell ref="C22:C25"/>
     <mergeCell ref="F18:F21"/>
     <mergeCell ref="C18:C21"/>
-    <mergeCell ref="AE14:AE17"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="F2:F5"/>
     <mergeCell ref="E6:E9"/>
-    <mergeCell ref="AF6:AF9"/>
+    <mergeCell ref="AH6:AH9"/>
     <mergeCell ref="B10:B13"/>
-    <mergeCell ref="AE10:AE13"/>
     <mergeCell ref="A18:A21"/>
     <mergeCell ref="F22:F25"/>
     <mergeCell ref="D18:D21"/>
-    <mergeCell ref="AF14:AF17"/>
     <mergeCell ref="A2:A5"/>
+    <mergeCell ref="AI22:AI25"/>
     <mergeCell ref="C2:C5"/>
-    <mergeCell ref="AF2:AF5"/>
+    <mergeCell ref="B6:B9"/>
     <mergeCell ref="E2:E5"/>
-    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="AH2:AH5"/>
     <mergeCell ref="A14:A17"/>
-    <mergeCell ref="AE6:AE9"/>
     <mergeCell ref="A10:A13"/>
+    <mergeCell ref="AI2:AI5"/>
     <mergeCell ref="A22:A25"/>
     <mergeCell ref="D14:D17"/>
     <mergeCell ref="E22:E25"/>
     <mergeCell ref="F14:F17"/>
-    <mergeCell ref="AF22:AF25"/>
+    <mergeCell ref="AI18:AI21"/>
+    <mergeCell ref="AI14:AI17"/>
     <mergeCell ref="C6:C9"/>
     <mergeCell ref="D10:D13"/>
+    <mergeCell ref="AH22:AH25"/>
     <mergeCell ref="F10:F13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/docs/tables/summary_all_objects_accuracy_f1_EN.xlsx
+++ b/docs/tables/summary_all_objects_accuracy_f1_EN.xlsx
@@ -804,7 +804,7 @@
       </c>
       <c r="AI2" s="5" t="inlineStr">
         <is>
-          <t>incomplete reference: the bus stop's far side (away from the road) wasn't scanned; part of the reference is a merge of 2 scans that don't align perfectly in places</t>
+          <t>incomplete reference: the bus shelter's far side (away from the road) wasn't scanned; part of the reference is a merge of 2 scans that don't align perfectly in places</t>
         </is>
       </c>
     </row>
@@ -2926,8 +2926,8 @@
   </sheetData>
   <mergeCells count="48">
     <mergeCell ref="AI10:AI13"/>
+    <mergeCell ref="E18:E21"/>
     <mergeCell ref="C14:C17"/>
-    <mergeCell ref="E18:E21"/>
     <mergeCell ref="E14:E17"/>
     <mergeCell ref="AH18:AH21"/>
     <mergeCell ref="B22:B25"/>
@@ -3004,6 +3004,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
